--- a/myprojects/GatiGo/GatiGo_DCF_Model.xlsx
+++ b/myprojects/GatiGo/GatiGo_DCF_Model.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{732A89ED-87C2-4D91-AE51-16E8D8A0D878}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="30936" windowHeight="18696" tabRatio="500" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="HOME" sheetId="1" r:id="rId1"/>
@@ -1146,50 +1146,50 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1464,22 +1464,22 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
-      <c r="D1" s="65"/>
-      <c r="E1" s="65"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
+      <c r="D1" s="63"/>
+      <c r="E1" s="63"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="58" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
@@ -1499,13 +1499,13 @@
       </c>
     </row>
     <row r="4" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="67" t="s">
+      <c r="A4" s="59" t="s">
         <v>7</v>
       </c>
-      <c r="B4" s="67"/>
-      <c r="C4" s="67"/>
-      <c r="D4" s="67"/>
-      <c r="E4" s="67"/>
+      <c r="B4" s="59"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
     </row>
     <row r="5" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="7" t="s">
@@ -1607,13 +1607,13 @@
       </c>
     </row>
     <row r="10" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="68" t="s">
+      <c r="A10" s="60" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
+      <c r="B10" s="60"/>
+      <c r="C10" s="60"/>
+      <c r="D10" s="60"/>
+      <c r="E10" s="60"/>
     </row>
     <row r="11" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="10" t="s">
@@ -1676,13 +1676,13 @@
       </c>
     </row>
     <row r="14" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55" t="s">
+      <c r="A14" s="61" t="s">
         <v>26</v>
       </c>
-      <c r="B14" s="55"/>
-      <c r="C14" s="55"/>
-      <c r="D14" s="55"/>
-      <c r="E14" s="55"/>
+      <c r="B14" s="61"/>
+      <c r="C14" s="61"/>
+      <c r="D14" s="61"/>
+      <c r="E14" s="61"/>
     </row>
     <row r="15" spans="1:5" ht="36.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
@@ -1739,13 +1739,13 @@
       </c>
     </row>
     <row r="19" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64" t="s">
+      <c r="A19" s="62" t="s">
         <v>33</v>
       </c>
-      <c r="B19" s="64"/>
-      <c r="C19" s="64"/>
-      <c r="D19" s="64"/>
-      <c r="E19" s="64"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
     </row>
     <row r="20" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="17" t="s">
@@ -1865,15 +1865,15 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="59" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -1903,32 +1903,32 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>214</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
-      <c r="F1" s="69"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
     </row>
     <row r="2" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
-      <c r="F2" s="66"/>
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
     </row>
     <row r="3" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="64" t="s">
+      <c r="A3" s="62" t="s">
         <v>48</v>
       </c>
-      <c r="B3" s="64"/>
-      <c r="C3" s="64"/>
-      <c r="D3" s="64"/>
-      <c r="E3" s="64"/>
-      <c r="F3" s="64"/>
+      <c r="B3" s="62"/>
+      <c r="C3" s="62"/>
+      <c r="D3" s="62"/>
+      <c r="E3" s="62"/>
+      <c r="F3" s="62"/>
     </row>
     <row r="4" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="18" t="s">
@@ -1971,14 +1971,14 @@
       </c>
     </row>
     <row r="6" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="64" t="s">
+      <c r="A6" s="62" t="s">
         <v>55</v>
       </c>
-      <c r="B6" s="64"/>
-      <c r="C6" s="64"/>
-      <c r="D6" s="64"/>
-      <c r="E6" s="64"/>
-      <c r="F6" s="64"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="62"/>
+      <c r="D6" s="62"/>
+      <c r="E6" s="62"/>
+      <c r="F6" s="62"/>
     </row>
     <row r="7" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="18" t="s">
@@ -2061,14 +2061,14 @@
       </c>
     </row>
     <row r="11" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="64" t="s">
+      <c r="A11" s="62" t="s">
         <v>63</v>
       </c>
-      <c r="B11" s="64"/>
-      <c r="C11" s="64"/>
-      <c r="D11" s="64"/>
-      <c r="E11" s="64"/>
-      <c r="F11" s="64"/>
+      <c r="B11" s="62"/>
+      <c r="C11" s="62"/>
+      <c r="D11" s="62"/>
+      <c r="E11" s="62"/>
+      <c r="F11" s="62"/>
     </row>
     <row r="12" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="18" t="s">
@@ -2091,14 +2091,14 @@
       </c>
     </row>
     <row r="13" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="64" t="s">
+      <c r="A13" s="62" t="s">
         <v>66</v>
       </c>
-      <c r="B13" s="64"/>
-      <c r="C13" s="64"/>
-      <c r="D13" s="64"/>
-      <c r="E13" s="64"/>
-      <c r="F13" s="64"/>
+      <c r="B13" s="62"/>
+      <c r="C13" s="62"/>
+      <c r="D13" s="62"/>
+      <c r="E13" s="62"/>
+      <c r="F13" s="62"/>
     </row>
     <row r="14" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="18" t="s">
@@ -2121,14 +2121,14 @@
       </c>
     </row>
     <row r="15" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="64" t="s">
+      <c r="A15" s="62" t="s">
         <v>69</v>
       </c>
-      <c r="B15" s="64"/>
-      <c r="C15" s="64"/>
-      <c r="D15" s="64"/>
-      <c r="E15" s="64"/>
-      <c r="F15" s="64"/>
+      <c r="B15" s="62"/>
+      <c r="C15" s="62"/>
+      <c r="D15" s="62"/>
+      <c r="E15" s="62"/>
+      <c r="F15" s="62"/>
     </row>
     <row r="16" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="18" t="s">
@@ -2151,14 +2151,14 @@
       </c>
     </row>
     <row r="17" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="64" t="s">
+      <c r="A17" s="62" t="s">
         <v>72</v>
       </c>
-      <c r="B17" s="64"/>
-      <c r="C17" s="64"/>
-      <c r="D17" s="64"/>
-      <c r="E17" s="64"/>
-      <c r="F17" s="64"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="62"/>
+      <c r="D17" s="62"/>
+      <c r="E17" s="62"/>
+      <c r="F17" s="62"/>
     </row>
     <row r="18" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="18" t="s">
@@ -2219,14 +2219,14 @@
       </c>
     </row>
     <row r="21" spans="1:6" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="64" t="s">
+      <c r="A21" s="62" t="s">
         <v>77</v>
       </c>
-      <c r="B21" s="64"/>
-      <c r="C21" s="64"/>
-      <c r="D21" s="64"/>
-      <c r="E21" s="64"/>
-      <c r="F21" s="64"/>
+      <c r="B21" s="62"/>
+      <c r="C21" s="62"/>
+      <c r="D21" s="62"/>
+      <c r="E21" s="62"/>
+      <c r="F21" s="62"/>
     </row>
     <row r="22" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="18" t="s">
@@ -2249,30 +2249,30 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="58" t="s">
+      <c r="A24" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="59" t="s">
+      <c r="B24" s="55"/>
+      <c r="C24" s="55"/>
+      <c r="D24" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="E24" s="59"/>
-      <c r="F24" s="59"/>
+      <c r="E24" s="56"/>
+      <c r="F24" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A3:F3"/>
-    <mergeCell ref="A6:F6"/>
-    <mergeCell ref="A11:F11"/>
     <mergeCell ref="A13:F13"/>
     <mergeCell ref="A15:F15"/>
     <mergeCell ref="A17:F17"/>
     <mergeCell ref="A21:F21"/>
     <mergeCell ref="A24:C24"/>
     <mergeCell ref="D24:F24"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A11:F11"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -2290,13 +2290,13 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>215</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="53"/>
@@ -2306,13 +2306,13 @@
       <c r="E2" s="54"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="59" t="s">
         <v>81</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="7" t="s">
@@ -2354,13 +2354,13 @@
       </c>
     </row>
     <row r="6" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="68" t="s">
+      <c r="A6" s="60" t="s">
         <v>84</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
+      <c r="B6" s="60"/>
+      <c r="C6" s="60"/>
+      <c r="D6" s="60"/>
+      <c r="E6" s="60"/>
     </row>
     <row r="7" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
@@ -2403,13 +2403,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="67" t="s">
+      <c r="A9" s="59" t="s">
         <v>87</v>
       </c>
-      <c r="B9" s="67"/>
-      <c r="C9" s="67"/>
-      <c r="D9" s="67"/>
-      <c r="E9" s="67"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -2512,13 +2512,13 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="61" t="s">
         <v>15</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
     </row>
     <row r="16" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
@@ -2561,13 +2561,13 @@
       </c>
     </row>
     <row r="18" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="64" t="s">
+      <c r="A18" s="62" t="s">
         <v>101</v>
       </c>
-      <c r="B18" s="64"/>
-      <c r="C18" s="64"/>
-      <c r="D18" s="64"/>
-      <c r="E18" s="64"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="62"/>
+      <c r="D18" s="62"/>
+      <c r="E18" s="62"/>
     </row>
     <row r="19" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="18" t="s">
@@ -2690,15 +2690,15 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A26" s="58" t="s">
+      <c r="A26" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B26" s="58"/>
-      <c r="C26" s="59" t="s">
+      <c r="B26" s="55"/>
+      <c r="C26" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D26" s="59"/>
-      <c r="E26" s="59"/>
+      <c r="D26" s="56"/>
+      <c r="E26" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="8">
@@ -2727,31 +2727,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="66" t="s">
+      <c r="A2" s="58" t="s">
         <v>114</v>
       </c>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="66"/>
-      <c r="E2" s="66"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="59" t="s">
         <v>115</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -2834,13 +2834,13 @@
       </c>
     </row>
     <row r="8" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="68" t="s">
+      <c r="A8" s="60" t="s">
         <v>122</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
+      <c r="B8" s="60"/>
+      <c r="C8" s="60"/>
+      <c r="D8" s="60"/>
+      <c r="E8" s="60"/>
     </row>
     <row r="9" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="10" t="s">
@@ -2883,13 +2883,13 @@
       </c>
     </row>
     <row r="11" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55" t="s">
+      <c r="A11" s="61" t="s">
         <v>127</v>
       </c>
-      <c r="B11" s="55"/>
-      <c r="C11" s="55"/>
-      <c r="D11" s="55"/>
-      <c r="E11" s="55"/>
+      <c r="B11" s="61"/>
+      <c r="C11" s="61"/>
+      <c r="D11" s="61"/>
+      <c r="E11" s="61"/>
     </row>
     <row r="12" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
@@ -2932,15 +2932,15 @@
       </c>
     </row>
     <row r="15" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="58"/>
-      <c r="C15" s="59" t="s">
+      <c r="B15" s="55"/>
+      <c r="C15" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D15" s="59"/>
-      <c r="E15" s="59"/>
+      <c r="D15" s="56"/>
+      <c r="E15" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="7">
@@ -2968,29 +2968,29 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="57" t="s">
         <v>131</v>
       </c>
-      <c r="B1" s="69"/>
-      <c r="C1" s="69"/>
-      <c r="D1" s="69"/>
-      <c r="E1" s="69"/>
+      <c r="B1" s="57"/>
+      <c r="C1" s="57"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
     </row>
     <row r="3" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="67" t="s">
+      <c r="A3" s="59" t="s">
         <v>132</v>
       </c>
-      <c r="B3" s="67"/>
-      <c r="C3" s="67"/>
-      <c r="D3" s="67"/>
-      <c r="E3" s="67"/>
+      <c r="B3" s="59"/>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
     </row>
     <row r="4" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
@@ -3013,13 +3013,13 @@
       </c>
     </row>
     <row r="5" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="68" t="s">
+      <c r="A5" s="60" t="s">
         <v>134</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
+      <c r="B5" s="60"/>
+      <c r="C5" s="60"/>
+      <c r="D5" s="60"/>
+      <c r="E5" s="60"/>
     </row>
     <row r="6" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
@@ -3079,13 +3079,13 @@
       </c>
     </row>
     <row r="9" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="64" t="s">
+      <c r="A9" s="62" t="s">
         <v>140</v>
       </c>
-      <c r="B9" s="64"/>
-      <c r="C9" s="64"/>
-      <c r="D9" s="64"/>
-      <c r="E9" s="64"/>
+      <c r="B9" s="62"/>
+      <c r="C9" s="62"/>
+      <c r="D9" s="62"/>
+      <c r="E9" s="62"/>
     </row>
     <row r="10" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
@@ -3126,13 +3126,13 @@
       </c>
     </row>
     <row r="12" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="62" t="s">
+      <c r="A12" s="65" t="s">
         <v>145</v>
       </c>
-      <c r="B12" s="62"/>
-      <c r="C12" s="62"/>
-      <c r="D12" s="62"/>
-      <c r="E12" s="62"/>
+      <c r="B12" s="65"/>
+      <c r="C12" s="65"/>
+      <c r="D12" s="65"/>
+      <c r="E12" s="65"/>
     </row>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="36" t="s">
@@ -3207,13 +3207,13 @@
       </c>
     </row>
     <row r="17" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55" t="s">
+      <c r="A17" s="61" t="s">
         <v>154</v>
       </c>
-      <c r="B17" s="55"/>
-      <c r="C17" s="55"/>
-      <c r="D17" s="55"/>
-      <c r="E17" s="55"/>
+      <c r="B17" s="61"/>
+      <c r="C17" s="61"/>
+      <c r="D17" s="61"/>
+      <c r="E17" s="61"/>
     </row>
     <row r="18" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="7" t="s">
@@ -3305,13 +3305,13 @@
       </c>
     </row>
     <row r="23" spans="1:5" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="68" t="s">
+      <c r="A23" s="60" t="s">
         <v>163</v>
       </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
+      <c r="B23" s="60"/>
+      <c r="C23" s="60"/>
+      <c r="D23" s="60"/>
+      <c r="E23" s="60"/>
     </row>
     <row r="24" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="27" t="s">
@@ -3350,28 +3350,28 @@
       </c>
     </row>
     <row r="27" spans="1:5" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="59" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="D27" s="59"/>
-      <c r="E27" s="59"/>
+      <c r="D27" s="56"/>
+      <c r="E27" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A12:E12"/>
+    <mergeCell ref="A17:E17"/>
+    <mergeCell ref="A23:E23"/>
+    <mergeCell ref="A27:B27"/>
+    <mergeCell ref="C27:E27"/>
     <mergeCell ref="A1:E1"/>
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A3:E3"/>
     <mergeCell ref="A5:E5"/>
     <mergeCell ref="A9:E9"/>
-    <mergeCell ref="A12:E12"/>
-    <mergeCell ref="A17:E17"/>
-    <mergeCell ref="A23:E23"/>
-    <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:E27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3388,50 +3388,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="60" t="s">
+      <c r="A1" s="66" t="s">
         <v>168</v>
       </c>
-      <c r="B1" s="60"/>
-      <c r="C1" s="60"/>
-      <c r="D1" s="60"/>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="60"/>
-      <c r="H1" s="60"/>
+      <c r="B1" s="66"/>
+      <c r="C1" s="66"/>
+      <c r="D1" s="66"/>
+      <c r="E1" s="66"/>
+      <c r="F1" s="66"/>
+      <c r="G1" s="66"/>
+      <c r="H1" s="66"/>
     </row>
     <row r="2" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="61"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
-      <c r="D2" s="61"/>
-      <c r="E2" s="61"/>
-      <c r="F2" s="61"/>
-      <c r="G2" s="61"/>
-      <c r="H2" s="61"/>
+      <c r="A2" s="64"/>
+      <c r="B2" s="64"/>
+      <c r="C2" s="64"/>
+      <c r="D2" s="64"/>
+      <c r="E2" s="64"/>
+      <c r="F2" s="64"/>
+      <c r="G2" s="64"/>
+      <c r="H2" s="64"/>
     </row>
     <row r="3" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="62" t="s">
+      <c r="A3" s="65" t="s">
         <v>169</v>
       </c>
-      <c r="B3" s="62"/>
-      <c r="C3" s="62"/>
-      <c r="D3" s="62"/>
-      <c r="E3" s="62"/>
-      <c r="F3" s="62"/>
-      <c r="G3" s="62"/>
-      <c r="H3" s="62"/>
+      <c r="B3" s="65"/>
+      <c r="C3" s="65"/>
+      <c r="D3" s="65"/>
+      <c r="E3" s="65"/>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="63" t="s">
+      <c r="A4" s="67" t="s">
         <v>170</v>
       </c>
-      <c r="B4" s="63"/>
-      <c r="C4" s="63"/>
-      <c r="D4" s="63"/>
-      <c r="E4" s="63"/>
-      <c r="F4" s="63"/>
-      <c r="G4" s="63"/>
-      <c r="H4" s="63"/>
+      <c r="B4" s="67"/>
+      <c r="C4" s="67"/>
+      <c r="D4" s="67"/>
+      <c r="E4" s="67"/>
+      <c r="F4" s="67"/>
+      <c r="G4" s="67"/>
+      <c r="H4" s="67"/>
     </row>
     <row r="5" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
@@ -3625,40 +3625,40 @@
       </c>
     </row>
     <row r="13" spans="1:8" ht="24" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="57" t="s">
+      <c r="A13" s="68" t="s">
         <v>184</v>
       </c>
-      <c r="B13" s="57"/>
-      <c r="C13" s="57"/>
-      <c r="D13" s="57"/>
-      <c r="E13" s="57"/>
-      <c r="F13" s="57"/>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
+      <c r="B13" s="68"/>
+      <c r="C13" s="68"/>
+      <c r="D13" s="68"/>
+      <c r="E13" s="68"/>
+      <c r="F13" s="68"/>
+      <c r="G13" s="68"/>
+      <c r="H13" s="68"/>
     </row>
     <row r="15" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="55" t="s">
+      <c r="A15" s="61" t="s">
         <v>185</v>
       </c>
-      <c r="B15" s="55"/>
-      <c r="C15" s="55"/>
-      <c r="D15" s="55"/>
-      <c r="E15" s="55"/>
-      <c r="F15" s="55"/>
-      <c r="G15" s="55"/>
-      <c r="H15" s="55"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+      <c r="D15" s="61"/>
+      <c r="E15" s="61"/>
+      <c r="F15" s="61"/>
+      <c r="G15" s="61"/>
+      <c r="H15" s="61"/>
     </row>
     <row r="16" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="56" t="s">
+      <c r="A16" s="69" t="s">
         <v>186</v>
       </c>
-      <c r="B16" s="56"/>
-      <c r="C16" s="56"/>
-      <c r="D16" s="56"/>
-      <c r="E16" s="56"/>
-      <c r="F16" s="56"/>
-      <c r="G16" s="56"/>
-      <c r="H16" s="56"/>
+      <c r="B16" s="69"/>
+      <c r="C16" s="69"/>
+      <c r="D16" s="69"/>
+      <c r="E16" s="69"/>
+      <c r="F16" s="69"/>
+      <c r="G16" s="69"/>
+      <c r="H16" s="69"/>
     </row>
     <row r="17" spans="1:8" ht="18" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
@@ -3806,43 +3806,43 @@
       </c>
     </row>
     <row r="25" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="57" t="s">
+      <c r="A25" s="68" t="s">
         <v>198</v>
       </c>
-      <c r="B25" s="57"/>
-      <c r="C25" s="57"/>
-      <c r="D25" s="57"/>
-      <c r="E25" s="57"/>
-      <c r="F25" s="57"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="57"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="68"/>
+      <c r="G25" s="68"/>
+      <c r="H25" s="68"/>
     </row>
     <row r="27" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="55" t="s">
         <v>46</v>
       </c>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="59" t="s">
+      <c r="B27" s="55"/>
+      <c r="C27" s="55"/>
+      <c r="D27" s="55"/>
+      <c r="E27" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="F27" s="59"/>
-      <c r="G27" s="59"/>
-      <c r="H27" s="59"/>
+      <c r="F27" s="56"/>
+      <c r="G27" s="56"/>
+      <c r="H27" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="A15:H15"/>
+    <mergeCell ref="A16:H16"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="E27:H27"/>
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
     <mergeCell ref="A4:H4"/>
     <mergeCell ref="A13:H13"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A16:H16"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="E27:H27"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
@@ -3860,11 +3860,11 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:3" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="65" t="s">
+      <c r="A1" s="63" t="s">
         <v>199</v>
       </c>
-      <c r="B1" s="65"/>
-      <c r="C1" s="65"/>
+      <c r="B1" s="63"/>
+      <c r="C1" s="63"/>
     </row>
     <row r="2" spans="1:3" ht="75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="48"/>
@@ -3931,10 +3931,10 @@
     </row>
     <row r="10" spans="1:3" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="1"/>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="56" t="s">
         <v>47</v>
       </c>
-      <c r="C10" s="59"/>
+      <c r="C10" s="56"/>
     </row>
   </sheetData>
   <mergeCells count="2">
